--- a/data/gravel/Cannondale SuperSix Evo SE 2025.xlsx
+++ b/data/gravel/Cannondale SuperSix Evo SE 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4282A3-B01D-F145-A444-1E25EEF25040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5AE89B-D4F1-DC40-8200-B0193A1E371C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25340" yWindow="-22600" windowWidth="29680" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27400" yWindow="-18560" windowWidth="29680" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -269,9 +269,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>https://www.cannondale.com/en-us/bikes/road/gravel/superx</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -396,6 +393,12 @@
   </si>
   <si>
     <t>a8:g34</t>
+  </si>
+  <si>
+    <t>https://www.cannondale.com/en-us/bikes/road/gravel/supersix-evo-se</t>
+  </si>
+  <si>
+    <t>https://embed.widencdn.net/img/dorelrl/nup4udtkrk/1700px@1x/C21_C17102U_SuperSix_EVO_SE_MTG_PD.webp?color=f1edea&amp;q=99</t>
   </si>
 </sst>
 </file>
@@ -774,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -798,7 +801,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -806,7 +814,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -814,7 +822,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8">
         <v>46</v>
@@ -832,7 +840,7 @@
         <v>58</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" s="4">
         <v>46</v>
@@ -856,7 +864,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <f>VALUE(LEFT(J9,3))</f>
@@ -879,19 +887,19 @@
         <v>700</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O9" s="4"/>
     </row>
@@ -900,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <f>J10*10</f>
@@ -923,7 +931,7 @@
         <v>566</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J10" s="4">
         <v>44.9</v>
@@ -946,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C25" si="2">J11*10</f>
@@ -969,7 +977,7 @@
         <v>568</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J11" s="4">
         <v>50.7</v>
@@ -992,10 +1000,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -1008,7 +1016,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <f>J13</f>
@@ -1031,7 +1039,7 @@
         <v>71</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="4">
         <v>70</v>
@@ -1054,7 +1062,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14">
         <f>J14</f>
@@ -1077,7 +1085,7 @@
         <v>72.7</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J14" s="4">
         <v>73.900000000000006</v>
@@ -1100,7 +1108,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
@@ -1123,7 +1131,7 @@
         <v>843</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J15" s="4">
         <v>74.3</v>
@@ -1146,7 +1154,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <f t="shared" si="2"/>
@@ -1169,7 +1177,7 @@
         <v>175</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J16" s="4">
         <v>9.3000000000000007</v>
@@ -1192,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <f t="shared" si="2"/>
@@ -1215,7 +1223,7 @@
         <v>1048</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J17" s="4">
         <v>100.2</v>
@@ -1238,7 +1246,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
@@ -1261,7 +1269,7 @@
         <v>635</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J18" s="4">
         <v>59</v>
@@ -1284,7 +1292,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -1307,7 +1315,7 @@
         <v>422</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J19" s="4">
         <v>42.2</v>
@@ -1330,7 +1338,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -1353,7 +1361,7 @@
         <v>68</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" s="4">
         <v>7</v>
@@ -1376,7 +1384,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -1399,7 +1407,7 @@
         <v>262</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J21" s="4">
         <v>26</v>
@@ -1422,7 +1430,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -1445,7 +1453,7 @@
         <v>55</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J22" s="4">
         <v>5.5</v>
@@ -1468,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -1491,7 +1499,7 @@
         <v>62</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J23" s="4">
         <v>6.9</v>
@@ -1514,7 +1522,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -1537,7 +1545,7 @@
         <v>595</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J24" s="4">
         <v>51.5</v>
@@ -1560,7 +1568,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -1583,7 +1591,7 @@
         <v>392</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J25" s="4">
         <v>36.5</v>
@@ -1760,7 +1768,7 @@
         <v>75</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1838,7 +1846,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1892,7 +1900,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1954,13 +1962,16 @@
       <c r="A71" t="s">
         <v>67</v>
       </c>
+      <c r="B71">
+        <v>2725</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>68</v>
       </c>
       <c r="B72">
-        <v>4599</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1973,7 +1984,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Cannondale SuperSix Evo SE 2025.xlsx
+++ b/data/gravel/Cannondale SuperSix Evo SE 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5AE89B-D4F1-DC40-8200-B0193A1E371C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F333F23B-537E-F345-817D-E05ABE2CE796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27400" yWindow="-18560" windowWidth="29680" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>https://embed.widencdn.net/img/dorelrl/nup4udtkrk/1700px@1x/C21_C17102U_SuperSix_EVO_SE_MTG_PD.webp?color=f1edea&amp;q=99</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Wilton, Connecticut, USA</t>
   </si>
 </sst>
 </file>
@@ -758,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1987,6 +1993,14 @@
         <v>78</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Cannondale SuperSix Evo SE 2025.xlsx
+++ b/data/gravel/Cannondale SuperSix Evo SE 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F333F23B-537E-F345-817D-E05ABE2CE796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB644D4F-D994-5544-B87A-0C5D008D573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27400" yWindow="-18560" windowWidth="29680" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -405,6 +405,24 @@
   </si>
   <si>
     <t>Wilton, Connecticut, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -764,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1849,155 +1867,185 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B59">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="2"/>
+        <v>51</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="2"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B67" s="2"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B69" s="2"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71">
-        <v>2725</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72">
-        <v>4050</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>122</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>123</v>
       </c>
     </row>
